--- a/data/trans_dic/P15B_3_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P15B_3_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el trabajo en el último año</t>
+          <t>Población que ha tenido un accidente en el trabajo en el último año (tasa de respuesta: 89,08%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,67; 50,17</t>
+          <t>13,1; 50,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,12; 34,37</t>
+          <t>14,63; 34,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,22; 23,24</t>
+          <t>4,29; 21,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,14; 28,24</t>
+          <t>5,38; 28,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 16,56</t>
+          <t>2,08; 16,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,66</t>
+          <t>0,0; 6,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,85</t>
+          <t>0,0; 9,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,28; 7,25</t>
+          <t>1,29; 7,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,48; 24,82</t>
+          <t>7,58; 25,53</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,57; 15,64</t>
+          <t>6,54; 16,46</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,54; 11,44</t>
+          <t>2,48; 10,8</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,49; 12,4</t>
+          <t>3,2; 11,61</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>26,04; 48,48</t>
+          <t>27,5; 48,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,98; 28,3</t>
+          <t>15,4; 27,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,55; 26,39</t>
+          <t>12,02; 26,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19,24; 38,83</t>
+          <t>20,66; 38,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,42; 29,21</t>
+          <t>5,25; 29,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,7; 12,38</t>
+          <t>2,83; 12,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,47; 16,88</t>
+          <t>4,53; 16,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,56; 20,19</t>
+          <t>6,45; 18,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,89; 38,94</t>
+          <t>22,73; 39,38</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,01; 20,61</t>
+          <t>11,87; 20,1</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,1; 19,13</t>
+          <t>9,67; 19,39</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,01; 28,77</t>
+          <t>15,25; 27,58</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,43</t>
+          <t>0,0; 43,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,16; 39,09</t>
+          <t>7,09; 37,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,92</t>
+          <t>0,0; 29,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,51</t>
+          <t>0,0; 27,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,03</t>
+          <t>0,0; 52,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,79</t>
+          <t>0,0; 35,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,34; 28,31</t>
+          <t>3,37; 27,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,64</t>
+          <t>0,0; 14,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,12</t>
+          <t>3,03; 33,14</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,54; 29,99</t>
+          <t>7,36; 30,61</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,16; 22,05</t>
+          <t>4,55; 22,24</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,0; 15,4</t>
+          <t>1,2; 16,91</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24,11; 41,52</t>
+          <t>24,54; 40,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,13; 27,28</t>
+          <t>16,87; 26,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,09; 20,03</t>
+          <t>9,99; 19,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,11; 30,88</t>
+          <t>16,75; 30,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,29; 18,96</t>
+          <t>5,01; 18,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,72; 9,26</t>
+          <t>2,57; 9,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,25; 11,95</t>
+          <t>4,14; 11,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,75; 11,23</t>
+          <t>4,96; 11,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,09; 29,47</t>
+          <t>16,95; 28,63</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11,24; 17,4</t>
+          <t>11,17; 17,15</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,08; 14,18</t>
+          <t>8,06; 14,7</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,67; 19,11</t>
+          <t>11,32; 19,07</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el trabajo en el último año</t>
+          <t>Población que ha tenido un accidente en el trabajo en el último año (tasa de respuesta: 89,08%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3189; 12630</t>
+          <t>3298; 12614</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11600; 26374</t>
+          <t>11228; 26242</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1894; 10434</t>
+          <t>1925; 9782</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1829; 10056</t>
+          <t>1916; 10058</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>924; 7541</t>
+          <t>949; 7709</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 7527</t>
+          <t>0; 7100</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 7345</t>
+          <t>0; 7246</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1016; 5766</t>
+          <t>1024; 5747</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5290; 17549</t>
+          <t>5361; 18053</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12454; 29673</t>
+          <t>12396; 31226</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3029; 13676</t>
+          <t>2963; 12905</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4020; 14275</t>
+          <t>3687; 13366</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20446; 38058</t>
+          <t>21592; 38098</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29280; 51878</t>
+          <t>28225; 49994</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13875; 31699</t>
+          <t>14440; 31937</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24837; 50140</t>
+          <t>26676; 50239</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1901; 10236</t>
+          <t>1839; 10204</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3069; 14071</t>
+          <t>3221; 14135</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3835; 14491</t>
+          <t>3887; 14276</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6686; 20585</t>
+          <t>6575; 18949</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24852; 44214</t>
+          <t>25808; 44713</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>35653; 61212</t>
+          <t>35265; 59696</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18749; 39395</t>
+          <t>19915; 39941</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>37001; 66486</t>
+          <t>35248; 63724</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 8232</t>
+          <t>0; 8375</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1865; 10184</t>
+          <t>1847; 9769</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 7367</t>
+          <t>0; 9012</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 9140</t>
+          <t>0; 9063</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6887</t>
+          <t>0; 6926</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 10299</t>
+          <t>0; 10120</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1036; 8779</t>
+          <t>1046; 8637</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4518</t>
+          <t>0; 4516</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 11135</t>
+          <t>989; 10814</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4136; 16442</t>
+          <t>4037; 16783</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2568; 13630</t>
+          <t>2814; 13744</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1282; 9869</t>
+          <t>769; 10840</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>29670; 51103</t>
+          <t>30208; 50354</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>48994; 78043</t>
+          <t>48256; 76938</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19756; 39229</t>
+          <t>19569; 38531</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>33865; 61119</t>
+          <t>33153; 59617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4963; 17783</t>
+          <t>4703; 17075</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6941; 23649</t>
+          <t>6561; 23133</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8146; 22882</t>
+          <t>7920; 21957</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10097; 23852</t>
+          <t>10538; 24550</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>37066; 63918</t>
+          <t>36767; 62093</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>60870; 94229</t>
+          <t>60488; 92858</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>31303; 54913</t>
+          <t>31227; 56922</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>47897; 78398</t>
+          <t>46430; 78266</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P15B_3_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P15B_3_R-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,1; 50,11</t>
+          <t>12,65; 51,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,63; 34,2</t>
+          <t>15,25; 36,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,29; 21,79</t>
+          <t>4,21; 21,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,38; 28,25</t>
+          <t>4,83; 28,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,08; 16,93</t>
+          <t>2,1; 16,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,29</t>
+          <t>0,0; 6,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,71</t>
+          <t>0,0; 10,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,29; 7,22</t>
+          <t>1,17; 7,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,58; 25,53</t>
+          <t>7,27; 24,46</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,54; 16,46</t>
+          <t>6,58; 16,39</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,48; 10,8</t>
+          <t>2,33; 10,88</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,2; 11,61</t>
+          <t>3,38; 12,4</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,02%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>27,5; 48,53</t>
+          <t>27,41; 49,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,4; 27,28</t>
+          <t>15,44; 27,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,02; 26,59</t>
+          <t>11,75; 26,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20,66; 38,91</t>
+          <t>20,51; 38,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,25; 29,12</t>
+          <t>5,34; 28,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 12,43</t>
+          <t>2,87; 13,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,53; 16,63</t>
+          <t>4,48; 17,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,45; 18,59</t>
+          <t>6,49; 18,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22,73; 39,38</t>
+          <t>22,6; 39,51</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,87; 20,1</t>
+          <t>11,62; 20,32</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,67; 19,39</t>
+          <t>9,77; 20,11</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,25; 27,58</t>
+          <t>15,8; 27,46</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 45,75</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>7,12; 38,32</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 27,96</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 23,48</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>0,0; 43,17</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>7,09; 37,49</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 29,26</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 27,28</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 52,33</t>
-        </is>
-      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,17</t>
+          <t>0,0; 35,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,37; 27,85</t>
+          <t>3,17; 29,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,63</t>
+          <t>0,0; 13,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,03; 33,14</t>
+          <t>3,06; 33,7</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,36; 30,61</t>
+          <t>7,1; 30,13</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,55; 22,24</t>
+          <t>4,27; 20,36</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 16,91</t>
+          <t>1,58; 14,86</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,42%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24,54; 40,91</t>
+          <t>24,28; 42,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,87; 26,89</t>
+          <t>16,96; 26,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,99; 19,68</t>
+          <t>10,2; 20,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,75; 30,12</t>
+          <t>15,79; 29,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,01; 18,2</t>
+          <t>4,76; 18,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,57; 9,06</t>
+          <t>2,74; 9,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,14; 11,47</t>
+          <t>4,23; 11,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,96; 11,56</t>
+          <t>4,33; 10,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,95; 28,63</t>
+          <t>17,34; 28,92</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11,17; 17,15</t>
+          <t>11,27; 17,33</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,06; 14,7</t>
+          <t>8,18; 14,85</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,32; 19,07</t>
+          <t>11,1; 18,27</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5009</t>
+          <t>5074</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2682</t>
+          <t>2729</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7691</t>
+          <t>7803</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3298; 12614</t>
+          <t>3184; 12995</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11228; 26242</t>
+          <t>11707; 28309</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1925; 9782</t>
+          <t>1892; 9872</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1916; 10058</t>
+          <t>1829; 10708</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>949; 7709</t>
+          <t>957; 7588</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 7100</t>
+          <t>0; 7358</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 7246</t>
+          <t>0; 7813</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1024; 5747</t>
+          <t>990; 6432</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5361; 18053</t>
+          <t>5140; 17292</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12396; 31226</t>
+          <t>12473; 31088</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2963; 12905</t>
+          <t>2778; 13003</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3687; 13366</t>
+          <t>4139; 15171</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>37466</t>
+          <t>40162</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11766</t>
+          <t>12415</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>49232</t>
+          <t>52577</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21592; 38098</t>
+          <t>21520; 38731</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28225; 49994</t>
+          <t>28302; 50611</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14440; 31937</t>
+          <t>14109; 31507</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26676; 50239</t>
+          <t>28531; 53262</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1839; 10204</t>
+          <t>1872; 10004</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3221; 14135</t>
+          <t>3267; 15331</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3887; 14276</t>
+          <t>3848; 14608</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6575; 18949</t>
+          <t>7209; 19991</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25808; 44713</t>
+          <t>25667; 44865</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>35265; 59696</t>
+          <t>34501; 60344</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19915; 39941</t>
+          <t>20126; 41416</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>35248; 63724</t>
+          <t>39521; 68675</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2828</t>
+          <t>2977</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1323</t>
+          <t>1426</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4151</t>
+          <t>4403</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 8375</t>
+          <t>0; 8875</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1847; 9769</t>
+          <t>1854; 9984</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 9012</t>
+          <t>0; 8611</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 9063</t>
+          <t>0; 9784</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6926</t>
+          <t>0; 5713</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 10120</t>
+          <t>0; 10252</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1046; 8637</t>
+          <t>983; 9043</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4516</t>
+          <t>0; 4914</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>989; 10814</t>
+          <t>1000; 10999</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4037; 16783</t>
+          <t>3894; 16521</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2814; 13744</t>
+          <t>2640; 12585</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>769; 10840</t>
+          <t>1211; 11426</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>45303</t>
+          <t>48213</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>15772</t>
+          <t>16570</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>61075</t>
+          <t>64782</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>30208; 50354</t>
+          <t>29880; 51811</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>48256; 76938</t>
+          <t>48533; 75625</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19569; 38531</t>
+          <t>19983; 40105</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>33153; 59617</t>
+          <t>34524; 64476</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4703; 17075</t>
+          <t>4464; 16998</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6561; 23133</t>
+          <t>7005; 23025</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7920; 21957</t>
+          <t>8102; 22800</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10538; 24550</t>
+          <t>9996; 25125</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>36767; 62093</t>
+          <t>37616; 62717</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>60488; 92858</t>
+          <t>61040; 93855</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>31227; 56922</t>
+          <t>31693; 57503</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>46430; 78266</t>
+          <t>49891; 82087</t>
         </is>
       </c>
     </row>
